--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: pending first run on frontend-milestone-3-development. BB-05, E2E-01: not run (B1)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-05, E2E-01: not run (B1)</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: pending first run on frontend-milestone-3-development. BB-03: not run (needs a running RC, B2)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-03: not run (needs a running RC, B2)</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: pending run. IT-02 ConcurrentAcceptTests: skipped in CI (no test DB, B3), counts as Blocked</t>
+          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: skipped (CIVICCONNECT_TEST_DB not set), counts as Blocked (B3)</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>UT-01 StatusTransitionTests: pending run. BB-04, E2E-02: not run (not wired)</t>
+          <t>UT-01 StatusTransitionTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-04, E2E-02: not run (not wired)</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="U16" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: pending first run on frontend-milestone-3-development. IT-03: not run (no endpoint)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint)</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: pending first run on frontend-milestone-3-development. BB-05: not run (B1)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-05: not run (B1)</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="U30" s="5" t="inlineStr">
         <is>
-          <t>UT-03: pending run. IT-02: skipped in CI (B3), counts as Blocked</t>
+          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: skipped (CIVICCONNECT_TEST_DB not set), counts as Blocked (B3)</t>
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: pending first run on frontend-milestone-3-development. IT-03: not run (no endpoint)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint)</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -1877,12 +1877,12 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: skipped (CIVICCONNECT_TEST_DB not set), counts as Blocked (B3)</t>
+          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3)</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IN: IT-02 passes locally, not yet in CI (B3)</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="U30" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: skipped (CIVICCONNECT_TEST_DB not set), counts as Blocked (B3)</t>
+          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3)</t>
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>IN: IT-02 blocked (B3)</t>
+          <t>IN: IT-02 passes locally, not yet in CI (B3)</t>
         </is>
       </c>
     </row>

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-03: not run (needs a running RC, B2)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-03a to BB-03e: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>E2E-02 (walk-through)</t>
+          <t>AC-010.1 check, E2E-02 (walk-through)</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>Not run: needs a running RC (B2)</t>
+          <t>AC-010.1: Partial, requester and category not shown (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IN: AC-010.1 partial, DEF-001 (proposed, Minor)</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3)</t>
+          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3). AC-011.1 and AC-011.2 (UI): Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint). Out-of-scope accept refused, request unchanged: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>IN*: gap, comes with FR-012 wiring</t>
+          <t>IN*: gap, comes with FR-012 wiring; AC-014.2 reworded by CR-012 (proposed)</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>OUT: Scope Freeze v1.0</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
         </is>
       </c>
     </row>

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Not in app/ (Backend/ only). Request.Submit domain validation exists; no submit page</t>
+          <t>SubmissionService.SubmitAsync; Pages/Requests/Submit; POST /api/v1/requests; Request.Location and request_reference_seq (migration AddRequestLocation)</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>Not run: blocked by B1</t>
+          <t>UT-05 1/1, BB-01 5/5 and BB-02 4/4 passed in SubmissionServiceTests (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-001.1, AC-001.2, BB-02 (page) and IT-01 (manual API): Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). IT-01 automated and E2E-01: not run</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>IN*: blocked (B1, port requester slice)</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Category entity and seed (Domain/ReferenceData/Category.cs); no submit form</t>
+          <t>IRequestQueries.ListActiveCategoriesAsync feeds the Submit select from reference data; SubmissionService rejects unknown or retired categories</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>Not run: blocked by B1</t>
+          <t>UT-02 1/1 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-002.1 and AC-002.2: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>IN*: blocked (B1)</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Not in app/</t>
+          <t>Pages/Requests/Details (read only, policy View first); Shared/_RequestFields; StatusBadgeTagHelper</t>
         </is>
       </c>
       <c r="S5" s="5" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>Not run: blocked by B1</t>
+          <t>AC-003.1 and AC-003.2: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). E2E-01: not run</t>
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>IN*: blocked (B1)</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>RequestAccess.MayView requester rule; no history page</t>
+          <t>Pages/Requests/Index; RequestQueries.ListForRequesterAsync scoped to the requester; RequestAccess.MayView</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-05, E2E-01: not run (B1)</t>
+          <t>UT-04 RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-004.1: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). BB-05: not run (the seed has one requester). E2E-01: not run</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>IN*: page blocked (B1)</t>
+          <t>IN: BB-05 needs a second seeded requester</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Pages/Staff/Details.cshtml.cs (view checked by policy first)</t>
+          <t>Pages/Staff/Details with Shared/_RequestFields (requester, category, location), policy checked first</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>AC-010.1: Partial, requester and category not shown (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
+          <t>AC-010.1: Partial in round 1 (DEF-001); retest Pass after the fix (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>IN: AC-010.1 partial, DEF-001 (proposed, Minor)</t>
+          <t>IN: DEF-001 fixed</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Domain/Requests/StatusTransition; StatusTransitionService.MoveAsync; not wired to a page or endpoint</t>
+          <t>StatusTransitionService.MoveAsync wired to Pages/Staff/Details (next-status form) and PATCH /api/v1/requests/{id}/status</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>UT-01 StatusTransitionTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-04, E2E-02: not run (not wired)</t>
+          <t>UT-01 StatusTransitionTests 8/8 and StatusTransitionServiceTests 2/2 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-012.1 and AC-012.2 (BB-04 flow): Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). E2E-02: not run</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>IN*: gap, wire status endpoint and page actions</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>RequestAccess.MayWorkOn (owning, in-scope staff); no close flow yet</t>
+          <t>Close checked as its own action (RequestAction.Close, RequestAccess.MayWorkOn); resolution note stored on the history entry</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="U16" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint)</t>
+          <t>UT-04 StatusTransitionServiceTests 2/2 and RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-014.2 and IT-03 (manual API, 403): Pass. AC-014.1: Partial, no requester feedback because FR-007 is not built (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>IN*: gap, comes with FR-012 wiring; AC-014.2 reworded by CR-012 (proposed)</t>
+          <t>IN: AC-014.1 partial (FR-007); AC-014.2 reworded by CR-012 (proposed)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Not in app/ (needs the submit page)</t>
+          <t>Pages/Requests/Submit: title, description, location, category, submit (five steps)</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="U26" s="5" t="inlineStr">
         <is>
-          <t>Not run: blocked by B1</t>
+          <t>Walkthrough not run: needs a timed first-time user</t>
         </is>
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>IN*: blocked (B1)</t>
+          <t>IN*: walkthrough pending (Role 1)</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>RequestAccess.MayView requester rule; Staff/Details 404 outside policy</t>
+          <t>RequestAccess.MayView; requester queries scoped to the requester; Requests/Details returns 404 outside the policy</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-05: not run (B1)</t>
+          <t>UT-04 RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). BB-05: not run (the seed has one requester)</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>IN*: page blocked (B1)</t>
+          <t>IN: BB-05 needs a second seeded requester</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03: not run (no endpoint). Out-of-scope accept refused, request unchanged: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
+          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03 (manual): 403 for Staff Two and the requester (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). Out-of-scope accept refused, request unchanged: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -522,7 +522,7 @@
     <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CivicConnect Requirements Traceability Matrix (RTM) - M3 release candidate (live) - v3.0</t>
+          <t>CivicConnect Requirements Traceability Matrix (RTM) - M3 release candidate (live) - v3.0. Evidence: 76/76 automated tests pass locally on the release candidate; integration and E2E tests skip in CI until it has a test database (B3). Acceptance: Test/Evidence/M3_Acceptance_Checks.md</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>SubmissionService.SubmitAsync; Pages/Requests/Submit; POST /api/v1/requests; Request.Location and request_reference_seq (migration AddRequestLocation)</t>
+          <t>SubmissionService; Pages/Requests/Submit; POST /api/v1/requests; Location and reference sequence (migration AddStaffScopesLocationAndReferences)</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>UT-05 1/1, BB-01 5/5 and BB-02 4/4 passed in SubmissionServiceTests (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-001.1, AC-001.2, BB-02 (page) and IT-01 (manual API): Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). IT-01 automated and E2E-01: not run</t>
+          <t>UT-05, BB-01, BB-02, IT-01, E2E-01 pass (automated). AC-001.1, AC-001.2, BB-02 pass (acceptance)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>UT-02 1/1 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-002.1 and AC-002.2: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
+          <t>UT-02 pass (automated). AC-002.1, AC-002.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>AC-003.1 and AC-003.2: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). E2E-01: not run</t>
+          <t>E2E-01 pass (automated). AC-003.1, AC-003.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-004.1: Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). BB-05: not run (the seed has one requester). E2E-01: not run</t>
+          <t>BB-05, E2E-01 pass (automated). AC-004.1, BB-05 pass (acceptance)</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>IN: BB-05 needs a second seeded requester</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Not in app/</t>
+          <t>Assignment and status changes write RequesterFeedback; Pages/Requests/Details lists the updates</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>A feedback item with a timestamp appears for the requester after a status change</t>
+          <t>A timestamped update for each change, shown on the requester's next visit</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
         <is>
-          <t>Not run: blocked by B1 and FR-012 wiring</t>
+          <t>E2E-02 pass (automated). AC-007.1 pass (acceptance). AC-007.2 not built (CR-009)</t>
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>IN* (stretch): blocked (B1)</t>
+          <t>IN: AC-007.2 deferred (CR-009)</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Pages/Staff/Queue.cshtml.cs scoped query; Domain/Access/StaffCategoryScope; AuthorisationPolicy with RequestAccess.MayView; Staff/Details returns 404 outside scope</t>
+          <t>IQueueRepository and Staff/Queue scoped by category; scope check in AuthorisationPolicy; Staff/Details 404 outside scope</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>UT-04, BB-03</t>
+          <t>UT-04, BB-03, QueueTests</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). BB-03a to BB-03e: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
+          <t>UT-04, QueueTests pass (automated). BB-03a to BB-03e pass (acceptance)</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>IN: B4 closed by category scope</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1638,27 +1638,27 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>IQueueRepository.SearchAsync (filter, search, sort, paging); GET /api/v1/queue; Staff/Queue filter bar</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>QueueTests, ApiTests, StaffScreensTests</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Only matching requests in the staff member's scope, in the chosen order; a message when none match</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>QueueTests, ApiTests, StaffScreensTests pass (automated). Search and filter pass (acceptance)</t>
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN: built after the freeze; remove from CR-013</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>AC-010.1: Partial in round 1 (DEF-001); retest Pass after the fix (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
+          <t>AC-010.1 pass (acceptance); DEF-001 fixed</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>IN: DEF-001 fixed</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3). AC-011.1 and AC-011.2 (UI): Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
+          <t>UT-03, IT-02, eight-staff API race pass (automated). AC-011.1, AC-011.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>IN: IT-02 passes locally, not yet in CI (B3)</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>StatusTransitionService.MoveAsync wired to Pages/Staff/Details (next-status form) and PATCH /api/v1/requests/{id}/status</t>
+          <t>StatusTransitionService.MoveAsync; Staff/Details status form; POST /api/v1/requests/{id}/status</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>UT-01 StatusTransitionTests 8/8 and StatusTransitionServiceTests 2/2 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-012.1 and AC-012.2 (BB-04 flow): Pass (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). E2E-02: not run</t>
+          <t>UT-01, StatusTransitionServiceTests, LifecycleTests, E2E-02 pass (automated). AC-012.1, AC-012.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2086,27 +2086,27 @@
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>NoteService; POST /api/v1/requests/{id}/notes; Staff/Details add-note form</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NoteServiceTests, ApiTests, StaffScreensTests</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>A note is saved to the history with author and time and is never edited</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>NoteServiceTests, ApiTests, StaffScreensTests pass (automated). Add a note pass (acceptance)</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN: built after the freeze; remove from CR-013</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Close checked as its own action (RequestAction.Close, RequestAccess.MayWorkOn); resolution note stored on the history entry</t>
+          <t>Close checked as its own action: the owner in scope or an administrator (CR-012); resolving needs a note</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="U16" s="5" t="inlineStr">
         <is>
-          <t>UT-04 StatusTransitionServiceTests 2/2 and RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). AC-014.2 and IT-03 (manual API, 403): Pass. AC-014.1: Partial, no requester feedback because FR-007 is not built (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12)</t>
+          <t>IT-03, E2E-02, AuthorisationTests pass (automated). AC-014.1, AC-014.2, administrator close pass (acceptance)</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>IN: AC-014.1 partial (FR-007); AC-014.2 reworded by CR-012 (proposed)</t>
+          <t>IN: AC-014.2 reworded by CR-012 (proposed)</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests 12/12 passed (local dotnet test, 2026-10-12, Release, 593e739 plus the requester port; 42 passed, 0 skipped). BB-05: not run (the seed has one requester)</t>
+          <t>UT-04, BB-05 pass (automated). BB-05 pass (acceptance)</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>IN: BB-05 needs a second seeded requester</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Staff queue query (indexed, capped at 50 rows)</t>
+          <t>IQueueRepository query, indexed and paged at 20 rows</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>PT-01</t>
+          <t>PT-01, QueueTests</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="U29" s="5" t="inlineStr">
         <is>
-          <t>Not run: no staging RC (B2)</t>
+          <t>PT-01 pass: p95 0.064 s with 5 users, 0 errors (Test/Evidence/PT-01_Results.md). QueueTests 1,000-request check pass</t>
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>IN*: blocked (B2)</t>
+          <t>IN: measured locally; staging pending (B2)</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="U30" s="5" t="inlineStr">
         <is>
-          <t>UT-03 AssignmentServiceTests: 4/4 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-02 ConcurrentAcceptTests: passed against local PostgreSQL 17 (dotnet test, 2026-10-12, eeb9362 plus the ConcurrentAcceptTests scope fix; 21 total: 21 passed, 0 skipped). Still skipped in CI until CI has a test database (B3)</t>
+          <t>UT-03, IT-02, eight-staff API race pass (automated)</t>
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>IN: IT-02 passes locally, not yet in CI (B3)</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>UT-04 RequestAccessTests: 8/8 passed (local dotnet test, 2026-10-12, commit 0339355, .NET 10.0.12 (21 total: 20 passed, 0 failed, 1 skipped)). IT-03 (manual): 403 for Staff Two and the requester (Test/Evidence/M3_Acceptance_Checks.md round 2, 2026-10-12). Out-of-scope accept refused, request unchanged: Pass (Test/Evidence/M3_Acceptance_Checks.md, local Development build, 2026-10-12)</t>
+          <t>UT-04, IT-03, AuthorisationTests pass (automated). Out-of-scope accept refused, AC-014.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>IN: built after the freeze; remove from CR-013</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>StatusTransitionService.MoveAsync; Staff/Details status form; POST /api/v1/requests/{id}/status</t>
+          <t>StatusTransitionService.MoveAsync; Staff/Details status form; POST /api/v1/requests/{id}/status (POST, not PATCH: CR-015)</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>IN: built after the freeze; remove from CR-013</t>
+          <t>IN</t>
         </is>
       </c>
     </row>

--- a/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
+++ b/Docs/Risks/RTM/CivicConnect-RTM-v3.0.xlsx
@@ -522,7 +522,7 @@
     <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CivicConnect Requirements Traceability Matrix (RTM) - M3 release candidate (live) - v3.0. Evidence: 76/76 automated tests pass locally on the release candidate; integration and E2E tests skip in CI until it has a test database (B3). Acceptance: Test/Evidence/M3_Acceptance_Checks.md</t>
+          <t>CivicConnect Requirements Traceability Matrix (RTM) - M3 release candidate (live) - v3.0. Evidence: 211/211 automated tests pass locally on 16 Oct 2026 against PostgreSQL 17. CI on main now runs the integration tests against PostgreSQL; the release candidate's own CI run follows its merge. Acceptance: Test/Evidence/M3_Acceptance_Checks.md</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="25.5" customHeight="1">
+    <row r="7" ht="42.25" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>FR-005</t>
@@ -1190,218 +1190,218 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pages/Requests/Index status filter; RequestQueries.ListForRequesterAsync filters on the requester and the status inside the query</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
+          <t>ManagementScreensTests (FR-005)</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>Only the requester's own requests with the chosen status are listed; a message when none match</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>ManagementScreensTests pass (automated, 16 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>IN (CR-016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80.5" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Attach supporting information to a request (e.g. a photo).</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ST-1, ST-2</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>AC-006.1</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ASR-05 (cost/complexity)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Not allocated (deferred)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Deferred - no design decision taken</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Deferred, storage not selected</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>PED Scope (Deferred); CR required to re-scope; RSK-003; RSK-018</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>at M3</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>at M3</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>at M3</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>at M4</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Candidate - may defer</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>K. Marota on re-scope</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>AttachmentService; RequestAttachment (JPG, PNG or PDF checked by file signature, 5 MB, 5 per request), stored in PostgreSQL (request_attachments); upload on Requests/Details and Staff/Details; GET /api/v1/requests/{id}/attachments/{attachmentId}</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>RequestAttachmentTests, AttachmentServiceTests, AttachmentTests, RequestAccessTests (FR-006)</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>An allowed file is stored and linked to the request; a disallowed type or size is refused with a message; only people who may view the request can download it</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>RequestAttachmentTests, AttachmentServiceTests, AttachmentTests pass (automated, 16 Oct 2026), including a renamed non-image file and a file over 5 MB refused</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="38.25" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Attach supporting information to a request (e.g. a photo).</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>ST-1, ST-2</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>AC-006.1</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>ASR-05 (cost/complexity)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Not allocated (deferred)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Deferred - no design decision taken</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Deferred, storage not selected</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>PED Scope (Deferred); CR required to re-scope; RSK-003; RSK-018</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>at M3</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>at M3</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>at M3</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
+    <row r="9" ht="67.75" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Receive feedback when a request is accepted, rejected, updated or completed.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ST-1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>AC-007.1; AC-007.2</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ASR-06; ASR-05</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Requests writes feedback with the status change -&gt; entry -&gt; FE</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>requests schema: feedback item in the same transaction as the status change</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>ADR-002 same-transaction write; in-app pull only, no push</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>ASP.NET Core on .NET 10 (C# 13); Npgsql with SQL migrations; PostgreSQL 17.x (ADR-003)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ADR-002; conflict C-4; CR-001; RSK-009; RSK-018</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Backend branch</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Core/Services/FeedbackService; Data/Migrations/004_feedback.sql; FeedbackController. No requester screen yet</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Not in CI: Backend NoteAndFeedbackTests (Nobody_can_mark_someone_elses_feedback_as_read). Planned: timing check</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>at M4</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>Candidate - may defer</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>K. Marota on re-scope</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38.25" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>FR-007</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Receive feedback when a request is accepted, rejected, updated or completed.</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>ST-1</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>AC-007.1; AC-007.2</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>ASR-06; ASR-05</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Requests writes feedback with the status change -&gt; entry -&gt; FE</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>requests schema: feedback item in the same transaction as the status change</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ADR-002 same-transaction write; in-app pull only, no push</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>ASP.NET Core on .NET 10 (C# 13); Npgsql with SQL migrations; PostgreSQL 17.x (ADR-003)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>ADR-002; conflict C-4; CR-001; RSK-009; RSK-018</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Backend branch</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Core/Services/FeedbackService; Data/Migrations/004_feedback.sql; FeedbackController. No requester screen yet</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>Not in CI: Backend NoteAndFeedbackTests (Nobody_can_mark_someone_elses_feedback_as_read). Planned: timing check</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>at M4</t>
-        </is>
-      </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Changed (CR-010)</t>
@@ -1414,27 +1414,27 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Assignment and status changes write RequesterFeedback; Pages/Requests/Details lists the updates</t>
+          <t>Assignment and status changes write RequesterFeedback; Pages/Requests/Details lists the updates; a rejection sends its reason to the requester (CR-009); status and updates refresh by polling every 5 s (NFR-002)</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>E2E-02</t>
+          <t>E2E-02, StatusTransitionServiceTests (AC-007.2), UpdatesPollingTests</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>A timestamped update for each change, shown on the requester's next visit</t>
+          <t>A timestamped update for each change, shown to the requester; a rejected request tells the requester why</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
         <is>
-          <t>E2E-02 pass (automated). AC-007.1 pass (acceptance). AC-007.2 not built (CR-009)</t>
+          <t>E2E-02, StatusTransitionServiceTests, UpdatesPollingTests pass (automated, 16 Oct 2026). AC-007.1 pass (acceptance)</t>
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>IN: AC-007.2 deferred (CR-009)</t>
+          <t>IN (AC-007.2 built by CR-009)</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="67.75" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>FR-011</t>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>AssignmentService.AcceptAsync; RequestRepository.TryAssignAsync; POST /api/v1/requests/{id}/assignment (409 when owned); Details OnPostAcceptAsync</t>
+          <t>AssignmentService.AcceptAsync; RequestRepository.TryAssignAsync; POST /api/v1/requests/{id}/assignment (409 when owned); Details OnPostAcceptAsync; Staff/Queue accept from the row (same AssignmentService)</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>UT-03, IT-02, E2E-02</t>
+          <t>UT-03, IT-02, E2E-02, StaffScreensTests (accept from the queue row)</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>UT-03, IT-02, eight-staff API race pass (automated). AC-011.1, AC-011.2 pass (acceptance)</t>
+          <t>UT-03, IT-02, eight-staff API race and StaffScreensTests (accept from the queue row, a second accept refused) pass (automated). AC-011.1, AC-011.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="38.25" customHeight="1">
+    <row r="14" ht="80.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>FR-012</t>
@@ -1974,22 +1974,22 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>StatusTransitionService.MoveAsync; Staff/Details status form; POST /api/v1/requests/{id}/status (POST, not PATCH: CR-015)</t>
+          <t>StatusTransitionService.MoveAsync; Staff/Details status form; POST /api/v1/requests/{id}/status (POST, not PATCH: CR-015); RejectAsync: Received to Rejected only, with a reason (CR-009); the database check constraints allow Rejected with no owner</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>UT-01, BB-04, E2E-02</t>
+          <t>UT-01, BB-04, E2E-02, StatusTransitionTests (Rejected)</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>Only forward adjacent moves allowed; Received to Closed and backward moves refused with a message; each change recorded with actor and timestamp</t>
+          <t>Only forward adjacent moves allowed; Received to Closed and backward moves refused with a message; Rejected only from Received; each change recorded with actor and timestamp</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>UT-01, StatusTransitionServiceTests, LifecycleTests, E2E-02 pass (automated). AC-012.1, AC-012.2 pass (acceptance)</t>
+          <t>UT-01, StatusTransitionTests (including Rejected), StatusTransitionServiceTests, LifecycleTests, E2E-02 pass (automated). AC-012.1, AC-012.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1">
+    <row r="17" ht="55" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>FR-015</t>
@@ -2310,31 +2310,31 @@
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>IOversightQueries.SummaryAsync; Pages/Oversight for managers and administrators: headline figures, counts by status and category, most recent requests</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ManagementScreensTests (FR-015), ReportingTests, RequestAccessTests</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Managers and administrators see activity figures that match the request records; other roles are refused</t>
         </is>
       </c>
       <c r="U17" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ManagementScreensTests, ReportingTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1">
+    <row r="18" ht="80.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>FR-016</t>
@@ -2422,31 +2422,31 @@
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Category.TargetResponseHours (default 72, set on Admin/Categories); Request.TargetResponseAtUtc fixed at submission (CR-005, migration AddRemainingRequirements); ResponseTarget.IsOverdue; Oversight Open and Overdue filter; overdue rows tagged on Oversight and Staff/Queue</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ResponseTargetTests, CategoryServiceTests, SubmissionServiceTests (FR-016), ReportingTests (AC-016.1, AC-016.2, CR-005), StaffScreensTests (AC-016.2)</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Open, resolved, closed and rejected requests are each identifiable; an open request past its target is flagged as overdue</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ResponseTargetTests, CategoryServiceTests, SubmissionServiceTests, ReportingTests, StaffScreensTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016; CR-005 approved)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="25.5" customHeight="1">
+    <row r="19" ht="42.25" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>FR-017</t>
@@ -2534,31 +2534,31 @@
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Oversight status, category and state filters; every figure and the performance table follow the same filter (OversightQueries)</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ManagementScreensTests, ReportingTests</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Counts by status and by category update together when a status, category or state is chosen</t>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ManagementScreensTests (counts follow the filters), ReportingTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="25.5" customHeight="1">
+    <row r="20" ht="67.75" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>FR-018</t>
@@ -2646,31 +2646,31 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Oversight service performance table by category (volumes, open, overdue, resolved, resolved within target, average hours to resolve); CSV export of the table and of the matching requests (CR-006)</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ReportingTests (AC-018.2, NFR-008)</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Performance figures in enough detail for accountability; the exported data matches what is displayed; only managers and administrators can export</t>
         </is>
       </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ReportingTests pass (automated, 16 Oct 2026): the exported table equals the displayed table row for row, and staff get 403</t>
         </is>
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016; CR-006 approved)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="38.25" customHeight="1">
+    <row r="21" ht="67.75" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>FR-019</t>
@@ -2758,31 +2758,31 @@
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>UserService (create, deactivate, reactivate; accounts never deleted); Admin/Users; AppUser.IsActive; AuthorisationPolicy and the development sign-in refuse deactivated users</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AppUserTests, UserServiceTests (FR-019), UserAdminTests (AC-019.1), LandingPageTests (AC-019.1), RoleMatrixTests</t>
         </is>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>An administrator creates or deactivates a user; a deactivated user can no longer sign in or act, from their next request</t>
         </is>
       </c>
       <c r="U21" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>AppUserTests, UserServiceTests, UserAdminTests, LandingPageTests, RoleMatrixTests pass (automated, 16 Oct 2026). Verified against the development sign-in only; real sign-in is CR-003</t>
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016); residual: real authentication under CR-003 (RSK-012)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="38.25" customHeight="1">
+    <row r="22" ht="55" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>FR-020</t>
@@ -2870,31 +2870,31 @@
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Not built in either tree; roles seeded only</t>
+          <t>UserService.ChangeRoleAsync and SetScopesAsync; Admin/Users; roles stored as data, permissions per role in AuthorisationPolicy (ADR-005); an administrator cannot change their own role</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>None (role-change rows dropped from UT-04)</t>
+          <t>UserServiceTests (FR-020, AC-020.2), UserAdminTests (AC-020.1, AC-020.2), RoleMatrixTests (TC-N006)</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>After a role change the user's permitted actions match the new role; a non-administrator cannot change roles</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>UserServiceTests, UserAdminTests, RoleMatrixTests pass (automated, 16 Oct 2026). Verified against the development sign-in only (CR-003)</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016); residual: real authentication under CR-003 (RSK-012)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="38.25" customHeight="1">
+    <row r="23" ht="42.25" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>FR-021</t>
@@ -2982,31 +2982,31 @@
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>CategoryService (add, rename, retire, restore, set target); Admin/Categories; the submit form reads the live list</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CategoryServiceTests (FR-021), ManagementScreensTests (FR-021)</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>An administrator changes the category list with no code change and the submit form follows; duplicate names refused</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>CategoryServiceTests, ManagementScreensTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>OUT: deferred to M4 by CR-013 (proposed), Scope Freeze v1.0</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="25.5" customHeight="1">
+    <row r="24" ht="42.25" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>FR-022</t>
@@ -3094,31 +3094,31 @@
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Admin/Audit combines request history with the insert-only audit_entries table (category, user and role changes), filtered by kind</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ManagementScreensTests (FR-022), UserAdminTests (FR-022), AttachmentTests</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Key controlled actions are listed with actor and time, for administrators only</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ManagementScreensTests, UserAdminTests, AttachmentTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="38.25" customHeight="1">
+    <row r="25" ht="42.25" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>FR-023</t>
@@ -3206,27 +3206,27 @@
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Sponsor role (CR-007); Pages/Reports/Summary reuses the oversight figures at summary level, with no individual requests</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ReportingTests (AC-023.1), RequestAccessTests (FR-023)</t>
         </is>
       </c>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Sponsors, managers and administrators see summary figures that match the records; sponsors see no request details</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ReportingTests, RequestAccessTests pass (automated, 16 Oct 2026)</t>
         </is>
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016; CR-007 approved)</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="25.5" customHeight="1">
+    <row r="27" ht="55" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>NFR-002</t>
@@ -3430,31 +3430,31 @@
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>status-poll.js refreshes the requester's status and updates every 5 s through the Requests/Details Updates handler (ADR-003 polling)</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>UpdatesPollingTests (NFR-002)</t>
         </is>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>A staff status change is visible on the requester's page within 15 s</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>UpdatesPollingTests pass (automated, 16 Oct 2026): the change appears in the next poll, well inside 15 s. Measured in process, not over a network</t>
         </is>
       </c>
       <c r="V27" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="25.5" customHeight="1">
+    <row r="28" ht="42.25" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>NFR-003</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>UT-04, BB-05</t>
+          <t>UT-04, BB-05, AttachmentTests, UpdatesPollingTests (NFR-003)</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>UT-04, BB-05 pass (automated). BB-05 pass (acceptance)</t>
+          <t>UT-04, BB-05, AttachmentTests, UpdatesPollingTests pass (automated). BB-05 pass (acceptance)</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="38.25" customHeight="1">
+    <row r="31" ht="55" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>NFR-006</t>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>UT-04, IT-03</t>
+          <t>UT-04, IT-03, RoleMatrixTests (TC-N006)</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>UT-04, IT-03, AuthorisationTests pass (automated). Out-of-scope accept refused, AC-014.2 pass (acceptance)</t>
+          <t>UT-04, IT-03, AuthorisationTests, RoleMatrixTests (every role against every action) pass (automated). Out-of-scope accept refused, AC-014.2 pass (acceptance)</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="38.25" customHeight="1">
+    <row r="32" ht="55" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>NFR-007</t>
@@ -3990,31 +3990,31 @@
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>request_history and audit_entries are insert-only, enforced by database triggers; every controlled action records its actor and time</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>HistoryInsertOnlyTests</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Key actions are recorded with actor and timestamp and cannot be silently altered or deleted</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>HistoryInsertOnlyTests pass (automated, 16 Oct 2026): an UPDATE or DELETE on request_history is refused. The audit_entries trigger has no test of its own yet</t>
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016); gap: no direct test of the audit_entries trigger</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="25.5" customHeight="1">
+    <row r="33" ht="42.25" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>NFR-008</t>
@@ -4102,27 +4102,27 @@
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Every oversight, summary and export figure is counted from the request rows with one filter (OversightQueries)</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ReportingTests (NFR-008, AC-018.2)</t>
         </is>
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Report figures, the list and the exports reconcile with the request records</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ReportingTests pass (automated, 16 Oct 2026): totals equal the database count and the category rows add up to the total row</t>
         </is>
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>OUT: not in M3 scope (Scope Freeze v1.0)</t>
+          <t>IN (CR-016)</t>
         </is>
       </c>
     </row>
